--- a/backend/uploads/public/smartpaw-products-template.xlsx
+++ b/backend/uploads/public/smartpaw-products-template.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P3"/>
+  <dimension ref="A1:Q3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -462,17 +462,18 @@
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
-    <col width="70" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="11" max="11"/>
     <col width="70" customWidth="1" min="12" max="12"/>
-    <col width="30" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="28" customWidth="1" min="16" max="16"/>
+    <col width="70" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="28" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -503,55 +504,60 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>product_type</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>pet_type</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>size</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>image_url</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>description_ka</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>tags</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>featured</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>slug</t>
         </is>
@@ -585,55 +591,60 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
+          <t>Only for food / hygiene. Food: dry-food | wet-food | snacks | other. Hygiene: teeth-care | grooming | pads | other</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>dog | cat | both  (default: both)</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>e.g. 2 kg, 12 kg, 250 ml — optional</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>Numeric price (e.g. 79.90)</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>Currency code, default GEL</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>Public URL to product image — will be downloaded &amp; hosted by us</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>REQUIRED · English description (up to 4000 chars)</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>Georgian description (optional)</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>Comma-separated tags, e.g. grain-free, large-breed</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>TRUE / FALSE (default FALSE)</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>draft | published (default published)</t>
         </is>
       </c>
-      <c r="P2" s="2" t="inlineStr">
+      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>Optional manual slug — auto-generated from name if blank</t>
         </is>
@@ -667,67 +678,75 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>dry-food</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>dog</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>15 kg</t>
         </is>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>219</v>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>GEL</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>https://images.unsplash.com/photo-1601758174039-bcdd2b9d2f3e?w=900</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Complete dry food for adult large-breed dogs (26–44 kg) from 15 months to 5 years.</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>სრულფასოვანი მშრალი საკვები მსხვილი ჯიშის ზრდასრული ძაღლებისთვის.</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>large-breed, adult, dry-food</t>
         </is>
       </c>
-      <c r="N3" t="b">
+      <c r="O3" t="b">
         <v>0</v>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>published</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
     </row>
   </sheetData>
-  <dataValidations count="5">
+  <dataValidations count="6">
     <dataValidation sqref="D3:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Allowed values: catalogue, specials" type="list">
       <formula1>"catalogue,specials"</formula1>
     </dataValidation>
     <dataValidation sqref="E3:E1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Allowed values: food, hygiene, vitamins, toys-accessories, innovation-tech, services" type="list">
       <formula1>"food,hygiene,vitamins,toys-accessories,innovation-tech,services"</formula1>
     </dataValidation>
-    <dataValidation sqref="F3:F1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Allowed values: dog, cat, both" type="list">
+    <dataValidation sqref="F3:F1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Allowed values: dry-food, wet-food, snacks, other, teeth-care, grooming, pads" type="list">
+      <formula1>"dry-food,wet-food,snacks,other,teeth-care,grooming,pads"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G3:G1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Allowed values: dog, cat, both" type="list">
       <formula1>"dog,cat,both"</formula1>
     </dataValidation>
-    <dataValidation sqref="O3:O1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Allowed values: draft, published" type="list">
+    <dataValidation sqref="P3:P1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Allowed values: draft, published" type="list">
       <formula1>"draft,published"</formula1>
     </dataValidation>
-    <dataValidation sqref="N3:N1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Allowed values: TRUE, FALSE" type="list">
+    <dataValidation sqref="O3:O1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Allowed values: TRUE, FALSE" type="list">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
   </dataValidations>
@@ -741,7 +760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -823,142 +842,154 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>pet_type</t>
+          <t>product_type</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>dog | cat | both  (default: both)</t>
+          <t>Only for food / hygiene. Food: dry-food | wet-food | snacks | other. Hygiene: teeth-care | grooming | pads | other</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>size</t>
+          <t>pet_type</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>e.g. 2 kg, 12 kg, 250 ml — optional</t>
+          <t>dog | cat | both  (default: both)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>price</t>
+          <t>size</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Numeric price (e.g. 79.90)</t>
+          <t>e.g. 2 kg, 12 kg, 250 ml — optional</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>price</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Currency code, default GEL</t>
+          <t>Numeric price (e.g. 79.90)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>image_url</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Public URL to product image — will be downloaded &amp; hosted by us</t>
+          <t>Currency code, default GEL</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>image_url</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>REQUIRED · English description (up to 4000 chars)</t>
+          <t>Public URL to product image — will be downloaded &amp; hosted by us</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>description_ka</t>
+          <t>description</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Georgian description (optional)</t>
+          <t>REQUIRED · English description (up to 4000 chars)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>tags</t>
+          <t>description_ka</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Comma-separated tags, e.g. grain-free, large-breed</t>
+          <t>Georgian description (optional)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>featured</t>
+          <t>tags</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>TRUE / FALSE (default FALSE)</t>
+          <t>Comma-separated tags, e.g. grain-free, large-breed</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>featured</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>draft | published (default published)</t>
+          <t>TRUE / FALSE (default FALSE)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>draft | published (default published)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>slug</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>Optional manual slug — auto-generated from name if blank</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>Tip</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>Rows are upserted by slug. If a slug already exists in the database the row UPDATES it; otherwise a new product is created. Delete the example row (row 3) before uploading your real data.</t>
         </is>
